--- a/ig/ekg/all-profiles.xlsx
+++ b/ig/ekg/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.2</t>
+    <t>2.0.0-trial-use-2026-04-28</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:08:45+00:00</t>
+    <t>2026-04-29T09:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1065,7 +1065,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-medcom-canonical-semver:The canonical SHALL include an explicit semantic version (semver) with optional prerelease (-...) and build metadata (+...). {matches('^.*[|][0-9]+[.][0-9]+([.][0-9]+)?(-[0-9A-Za-z-]+([.][0-9A-Za-z-]+)*)?([+][0-9A-Za-z-]+([.][0-9A-Za-z-]+)*)?$')}medcom-canonical-fixed-major:If a version is present in the canonical, MAJOR SHALL be a fixed value. {matches('^.*[|]1[.].*$')}</t>
+medcom-canonical-semver:The canonical SHALL include an explicit semantic version (semver) with optional prerelease (-...) and build metadata (+...). {matches('^.*[|][0-9]+[.][0-9]+([.][0-9]+)?(-[0-9A-Za-z-]+([.][0-9A-Za-z-]+)*)?([+][0-9A-Za-z-]+([.][0-9A-Za-z-]+)*)?$')}medcom-canonical-fixed-major:If a version is present in the canonical, MAJOR SHALL be a fixed value. {matches('^.*[|]2[.].*$')}</t>
   </si>
   <si>
     <t>Composition.meta.security</t>
@@ -2426,7 +2426,7 @@
 </t>
   </si>
   <si>
-    <t>Base64-encoded content of the EKG recording PDF/A document.</t>
+    <t>Base64-encoded content of the EKG recording PDF document.</t>
   </si>
   <si>
     <t>The actual data of the attachment - a sequence of bytes, base64 encoded.</t>
@@ -3292,7 +3292,7 @@
 </t>
   </si>
   <si>
-    <t>Free-text note, used to document relevant measurement-related remarks. Line breaks in FHIR string values must be represented as escaped newline characters \n in JSON and either as a literal newline in the element text or as the character reference &amp;#xA; in XML.</t>
+    <t>Free-text note, used to document relevant measurement-related remarks. Line breaks must be represented as escaped newline characters \n in JSON and as the character reference &amp;#xA; in XML.</t>
   </si>
   <si>
     <t>Comments about the observation or the results.</t>

--- a/ig/ekg/all-profiles.xlsx
+++ b/ig/ekg/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13458" uniqueCount="1271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13458" uniqueCount="1270">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-trial-use-2026-04-28</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:39:42+00:00</t>
+    <t>2026-06-04T11:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1964,7 +1964,7 @@
     <t>Composition.event.period.start</t>
   </si>
   <si>
-    <t>The end time of the EKG recording</t>
+    <t>The start time of the EKG recording</t>
   </si>
   <si>
     <t>The start of the period. The boundary is inclusive.</t>
@@ -1983,7 +1983,7 @@
     <t>Composition.event.period.end</t>
   </si>
   <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
+    <t>The end time of the EKG recording</t>
   </si>
   <si>
     <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
@@ -3038,9 +3038,6 @@
   </si>
   <si>
     <t>Observation.effective[x].start</t>
-  </si>
-  <si>
-    <t>The start time of the EKG recording</t>
   </si>
   <si>
     <t>Observation.effective[x]:effectivePeriod.end</t>
@@ -34481,7 +34478,7 @@
         <v>533</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>976</v>
+        <v>626</v>
       </c>
       <c r="N285" t="s" s="2">
         <v>627</v>
@@ -34557,10 +34554,10 @@
         <v>705</v>
       </c>
       <c r="B286" t="s" s="2">
+        <v>976</v>
+      </c>
+      <c r="C286" t="s" s="2">
         <v>977</v>
-      </c>
-      <c r="C286" t="s" s="2">
-        <v>978</v>
       </c>
       <c r="D286" s="2"/>
       <c r="E286" t="s" s="2">
@@ -34586,7 +34583,7 @@
         <v>533</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="N286" t="s" s="2">
         <v>633</v>
@@ -34664,10 +34661,10 @@
         <v>705</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="D287" s="2"/>
       <c r="E287" t="s" s="2">
@@ -34693,13 +34690,13 @@
         <v>125</v>
       </c>
       <c r="M287" t="s" s="2">
+        <v>979</v>
+      </c>
+      <c r="N287" t="s" s="2">
         <v>980</v>
       </c>
-      <c r="N287" t="s" s="2">
+      <c r="O287" t="s" s="2">
         <v>981</v>
-      </c>
-      <c r="O287" t="s" s="2">
-        <v>982</v>
       </c>
       <c r="P287" s="2"/>
       <c r="Q287" t="s" s="2">
@@ -34749,7 +34746,7 @@
         <v>74</v>
       </c>
       <c r="AG287" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AH287" t="s" s="2">
         <v>75</v>
@@ -34769,10 +34766,10 @@
         <v>705</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="D288" s="2"/>
       <c r="E288" t="s" s="2">
@@ -34795,17 +34792,17 @@
         <v>83</v>
       </c>
       <c r="L288" t="s" s="2">
+        <v>983</v>
+      </c>
+      <c r="M288" t="s" s="2">
         <v>984</v>
       </c>
-      <c r="M288" t="s" s="2">
+      <c r="N288" t="s" s="2">
         <v>985</v>
-      </c>
-      <c r="N288" t="s" s="2">
-        <v>986</v>
       </c>
       <c r="O288" s="2"/>
       <c r="P288" t="s" s="2">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="Q288" t="s" s="2">
         <v>74</v>
@@ -34854,7 +34851,7 @@
         <v>74</v>
       </c>
       <c r="AG288" t="s" s="2">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="AH288" t="s" s="2">
         <v>75</v>
@@ -34874,10 +34871,10 @@
         <v>705</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D289" s="2"/>
       <c r="E289" t="s" s="2">
@@ -34900,19 +34897,19 @@
         <v>83</v>
       </c>
       <c r="L289" t="s" s="2">
+        <v>988</v>
+      </c>
+      <c r="M289" t="s" s="2">
         <v>989</v>
       </c>
-      <c r="M289" t="s" s="2">
+      <c r="N289" t="s" s="2">
         <v>990</v>
       </c>
-      <c r="N289" t="s" s="2">
+      <c r="O289" t="s" s="2">
         <v>991</v>
       </c>
-      <c r="O289" t="s" s="2">
+      <c r="P289" t="s" s="2">
         <v>992</v>
-      </c>
-      <c r="P289" t="s" s="2">
-        <v>993</v>
       </c>
       <c r="Q289" t="s" s="2">
         <v>74</v>
@@ -34959,7 +34956,7 @@
         <v>171</v>
       </c>
       <c r="AG289" t="s" s="2">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="AH289" t="s" s="2">
         <v>75</v>
@@ -34968,7 +34965,7 @@
         <v>82</v>
       </c>
       <c r="AJ289" t="s" s="2">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AK289" t="s" s="2">
         <v>95</v>
@@ -34979,13 +34976,13 @@
         <v>705</v>
       </c>
       <c r="B290" t="s" s="2">
+        <v>994</v>
+      </c>
+      <c r="C290" t="s" s="2">
+        <v>987</v>
+      </c>
+      <c r="D290" t="s" s="2">
         <v>995</v>
-      </c>
-      <c r="C290" t="s" s="2">
-        <v>988</v>
-      </c>
-      <c r="D290" t="s" s="2">
-        <v>996</v>
       </c>
       <c r="E290" t="s" s="2">
         <v>74</v>
@@ -35007,19 +35004,19 @@
         <v>83</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="M290" t="s" s="2">
+        <v>989</v>
+      </c>
+      <c r="N290" t="s" s="2">
         <v>990</v>
       </c>
-      <c r="N290" t="s" s="2">
+      <c r="O290" t="s" s="2">
         <v>991</v>
       </c>
-      <c r="O290" t="s" s="2">
+      <c r="P290" t="s" s="2">
         <v>992</v>
-      </c>
-      <c r="P290" t="s" s="2">
-        <v>993</v>
       </c>
       <c r="Q290" t="s" s="2">
         <v>74</v>
@@ -35068,7 +35065,7 @@
         <v>74</v>
       </c>
       <c r="AG290" t="s" s="2">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="AH290" t="s" s="2">
         <v>75</v>
@@ -35077,7 +35074,7 @@
         <v>82</v>
       </c>
       <c r="AJ290" t="s" s="2">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AK290" t="s" s="2">
         <v>95</v>
@@ -35088,10 +35085,10 @@
         <v>705</v>
       </c>
       <c r="B291" t="s" s="2">
+        <v>997</v>
+      </c>
+      <c r="C291" t="s" s="2">
         <v>998</v>
-      </c>
-      <c r="C291" t="s" s="2">
-        <v>999</v>
       </c>
       <c r="D291" s="2"/>
       <c r="E291" t="s" s="2">
@@ -35191,10 +35188,10 @@
         <v>705</v>
       </c>
       <c r="B292" t="s" s="2">
+        <v>999</v>
+      </c>
+      <c r="C292" t="s" s="2">
         <v>1000</v>
-      </c>
-      <c r="C292" t="s" s="2">
-        <v>1001</v>
       </c>
       <c r="D292" s="2"/>
       <c r="E292" t="s" s="2">
@@ -35296,10 +35293,10 @@
         <v>705</v>
       </c>
       <c r="B293" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="C293" t="s" s="2">
         <v>1002</v>
-      </c>
-      <c r="C293" t="s" s="2">
-        <v>1003</v>
       </c>
       <c r="D293" s="2"/>
       <c r="E293" t="s" s="2">
@@ -35325,16 +35322,16 @@
         <v>201</v>
       </c>
       <c r="M293" t="s" s="2">
+        <v>1003</v>
+      </c>
+      <c r="N293" t="s" s="2">
         <v>1004</v>
       </c>
-      <c r="N293" t="s" s="2">
+      <c r="O293" t="s" s="2">
         <v>1005</v>
       </c>
-      <c r="O293" t="s" s="2">
+      <c r="P293" t="s" s="2">
         <v>1006</v>
-      </c>
-      <c r="P293" t="s" s="2">
-        <v>1007</v>
       </c>
       <c r="Q293" t="s" s="2">
         <v>74</v>
@@ -35383,7 +35380,7 @@
         <v>74</v>
       </c>
       <c r="AG293" t="s" s="2">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AH293" t="s" s="2">
         <v>75</v>
@@ -35403,10 +35400,10 @@
         <v>705</v>
       </c>
       <c r="B294" t="s" s="2">
+        <v>1008</v>
+      </c>
+      <c r="C294" t="s" s="2">
         <v>1009</v>
-      </c>
-      <c r="C294" t="s" s="2">
-        <v>1010</v>
       </c>
       <c r="D294" s="2"/>
       <c r="E294" t="s" s="2">
@@ -35432,20 +35429,20 @@
         <v>103</v>
       </c>
       <c r="M294" t="s" s="2">
+        <v>1010</v>
+      </c>
+      <c r="N294" t="s" s="2">
         <v>1011</v>
-      </c>
-      <c r="N294" t="s" s="2">
-        <v>1012</v>
       </c>
       <c r="O294" s="2"/>
       <c r="P294" t="s" s="2">
+        <v>1012</v>
+      </c>
+      <c r="Q294" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R294" t="s" s="2">
         <v>1013</v>
-      </c>
-      <c r="Q294" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R294" t="s" s="2">
-        <v>1014</v>
       </c>
       <c r="S294" t="s" s="2">
         <v>74</v>
@@ -35469,28 +35466,28 @@
         <v>121</v>
       </c>
       <c r="Z294" t="s" s="2">
+        <v>1014</v>
+      </c>
+      <c r="AA294" t="s" s="2">
         <v>1015</v>
       </c>
-      <c r="AA294" t="s" s="2">
+      <c r="AB294" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC294" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD294" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE294" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF294" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG294" t="s" s="2">
         <v>1016</v>
-      </c>
-      <c r="AB294" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC294" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD294" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE294" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF294" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG294" t="s" s="2">
-        <v>1017</v>
       </c>
       <c r="AH294" t="s" s="2">
         <v>75</v>
@@ -35510,10 +35507,10 @@
         <v>705</v>
       </c>
       <c r="B295" t="s" s="2">
+        <v>1017</v>
+      </c>
+      <c r="C295" t="s" s="2">
         <v>1018</v>
-      </c>
-      <c r="C295" t="s" s="2">
-        <v>1019</v>
       </c>
       <c r="D295" s="2"/>
       <c r="E295" t="s" s="2">
@@ -35539,14 +35536,14 @@
         <v>142</v>
       </c>
       <c r="M295" t="s" s="2">
+        <v>1019</v>
+      </c>
+      <c r="N295" t="s" s="2">
         <v>1020</v>
-      </c>
-      <c r="N295" t="s" s="2">
-        <v>1021</v>
       </c>
       <c r="O295" s="2"/>
       <c r="P295" t="s" s="2">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="Q295" t="s" s="2">
         <v>74</v>
@@ -35595,7 +35592,7 @@
         <v>74</v>
       </c>
       <c r="AG295" t="s" s="2">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AH295" t="s" s="2">
         <v>75</v>
@@ -35615,10 +35612,10 @@
         <v>705</v>
       </c>
       <c r="B296" t="s" s="2">
+        <v>1023</v>
+      </c>
+      <c r="C296" t="s" s="2">
         <v>1024</v>
-      </c>
-      <c r="C296" t="s" s="2">
-        <v>1025</v>
       </c>
       <c r="D296" s="2"/>
       <c r="E296" t="s" s="2">
@@ -35644,14 +35641,14 @@
         <v>97</v>
       </c>
       <c r="M296" t="s" s="2">
+        <v>1025</v>
+      </c>
+      <c r="N296" t="s" s="2">
         <v>1026</v>
-      </c>
-      <c r="N296" t="s" s="2">
-        <v>1027</v>
       </c>
       <c r="O296" s="2"/>
       <c r="P296" t="s" s="2">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="Q296" t="s" s="2">
         <v>74</v>
@@ -35661,55 +35658,55 @@
         <v>74</v>
       </c>
       <c r="T296" t="s" s="2">
+        <v>1028</v>
+      </c>
+      <c r="U296" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V296" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W296" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X296" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y296" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z296" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA296" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB296" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC296" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD296" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE296" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF296" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG296" t="s" s="2">
         <v>1029</v>
       </c>
-      <c r="U296" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V296" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W296" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X296" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y296" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z296" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA296" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB296" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC296" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD296" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE296" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF296" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG296" t="s" s="2">
+      <c r="AH296" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI296" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ296" t="s" s="2">
         <v>1030</v>
-      </c>
-      <c r="AH296" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI296" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ296" t="s" s="2">
-        <v>1031</v>
       </c>
       <c r="AK296" t="s" s="2">
         <v>95</v>
@@ -35720,10 +35717,10 @@
         <v>705</v>
       </c>
       <c r="B297" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="C297" t="s" s="2">
         <v>1032</v>
-      </c>
-      <c r="C297" t="s" s="2">
-        <v>1033</v>
       </c>
       <c r="D297" s="2"/>
       <c r="E297" t="s" s="2">
@@ -35749,16 +35746,16 @@
         <v>103</v>
       </c>
       <c r="M297" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="N297" t="s" s="2">
         <v>1034</v>
       </c>
-      <c r="N297" t="s" s="2">
+      <c r="O297" t="s" s="2">
         <v>1035</v>
       </c>
-      <c r="O297" t="s" s="2">
+      <c r="P297" t="s" s="2">
         <v>1036</v>
-      </c>
-      <c r="P297" t="s" s="2">
-        <v>1037</v>
       </c>
       <c r="Q297" t="s" s="2">
         <v>74</v>
@@ -35807,7 +35804,7 @@
         <v>74</v>
       </c>
       <c r="AG297" t="s" s="2">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="AH297" t="s" s="2">
         <v>75</v>
@@ -35827,10 +35824,10 @@
         <v>705</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D298" s="2"/>
       <c r="E298" t="s" s="2">
@@ -35856,16 +35853,16 @@
         <v>407</v>
       </c>
       <c r="M298" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="N298" t="s" s="2">
         <v>1040</v>
       </c>
-      <c r="N298" t="s" s="2">
+      <c r="O298" t="s" s="2">
         <v>1041</v>
       </c>
-      <c r="O298" t="s" s="2">
+      <c r="P298" t="s" s="2">
         <v>1042</v>
-      </c>
-      <c r="P298" t="s" s="2">
-        <v>1043</v>
       </c>
       <c r="Q298" t="s" s="2">
         <v>74</v>
@@ -35893,37 +35890,37 @@
         <v>340</v>
       </c>
       <c r="Z298" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="AA298" t="s" s="2">
         <v>1044</v>
       </c>
-      <c r="AA298" t="s" s="2">
+      <c r="AB298" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC298" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD298" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE298" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF298" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG298" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AH298" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI298" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ298" t="s" s="2">
         <v>1045</v>
-      </c>
-      <c r="AB298" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC298" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD298" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE298" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF298" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG298" t="s" s="2">
-        <v>1039</v>
-      </c>
-      <c r="AH298" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI298" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ298" t="s" s="2">
-        <v>1046</v>
       </c>
       <c r="AK298" t="s" s="2">
         <v>95</v>
@@ -35934,14 +35931,14 @@
         <v>705</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D299" s="2"/>
       <c r="E299" t="s" s="2">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F299" s="2"/>
       <c r="G299" t="s" s="2">
@@ -35963,16 +35960,16 @@
         <v>407</v>
       </c>
       <c r="M299" t="s" s="2">
+        <v>1048</v>
+      </c>
+      <c r="N299" t="s" s="2">
         <v>1049</v>
       </c>
-      <c r="N299" t="s" s="2">
+      <c r="O299" t="s" s="2">
         <v>1050</v>
       </c>
-      <c r="O299" t="s" s="2">
+      <c r="P299" t="s" s="2">
         <v>1051</v>
-      </c>
-      <c r="P299" t="s" s="2">
-        <v>1052</v>
       </c>
       <c r="Q299" t="s" s="2">
         <v>74</v>
@@ -36000,11 +35997,11 @@
         <v>340</v>
       </c>
       <c r="Z299" t="s" s="2">
+        <v>1052</v>
+      </c>
+      <c r="AA299" t="s" s="2">
         <v>1053</v>
       </c>
-      <c r="AA299" t="s" s="2">
-        <v>1054</v>
-      </c>
       <c r="AB299" t="s" s="2">
         <v>74</v>
       </c>
@@ -36021,7 +36018,7 @@
         <v>74</v>
       </c>
       <c r="AG299" t="s" s="2">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="AH299" t="s" s="2">
         <v>75</v>
@@ -36041,10 +36038,10 @@
         <v>705</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="D300" s="2"/>
       <c r="E300" t="s" s="2">
@@ -36067,19 +36064,19 @@
         <v>74</v>
       </c>
       <c r="L300" t="s" s="2">
+        <v>1055</v>
+      </c>
+      <c r="M300" t="s" s="2">
         <v>1056</v>
       </c>
-      <c r="M300" t="s" s="2">
+      <c r="N300" t="s" s="2">
         <v>1057</v>
       </c>
-      <c r="N300" t="s" s="2">
+      <c r="O300" t="s" s="2">
         <v>1058</v>
       </c>
-      <c r="O300" t="s" s="2">
+      <c r="P300" t="s" s="2">
         <v>1059</v>
-      </c>
-      <c r="P300" t="s" s="2">
-        <v>1060</v>
       </c>
       <c r="Q300" t="s" s="2">
         <v>74</v>
@@ -36128,7 +36125,7 @@
         <v>74</v>
       </c>
       <c r="AG300" t="s" s="2">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="AH300" t="s" s="2">
         <v>75</v>
@@ -36148,10 +36145,10 @@
         <v>705</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="D301" s="2"/>
       <c r="E301" t="s" s="2">
@@ -36251,10 +36248,10 @@
         <v>705</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="D302" s="2"/>
       <c r="E302" t="s" s="2">
@@ -36356,10 +36353,10 @@
         <v>705</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="D303" s="2"/>
       <c r="E303" t="s" s="2">
@@ -36382,16 +36379,16 @@
         <v>83</v>
       </c>
       <c r="L303" t="s" s="2">
+        <v>1063</v>
+      </c>
+      <c r="M303" t="s" s="2">
         <v>1064</v>
       </c>
-      <c r="M303" t="s" s="2">
+      <c r="N303" t="s" s="2">
         <v>1065</v>
       </c>
-      <c r="N303" t="s" s="2">
+      <c r="O303" t="s" s="2">
         <v>1066</v>
-      </c>
-      <c r="O303" t="s" s="2">
-        <v>1067</v>
       </c>
       <c r="P303" s="2"/>
       <c r="Q303" t="s" s="2">
@@ -36441,7 +36438,7 @@
         <v>74</v>
       </c>
       <c r="AG303" t="s" s="2">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="AH303" t="s" s="2">
         <v>75</v>
@@ -36461,10 +36458,10 @@
         <v>705</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="D304" s="2"/>
       <c r="E304" t="s" s="2">
@@ -36490,10 +36487,10 @@
         <v>533</v>
       </c>
       <c r="M304" t="s" s="2">
+        <v>1069</v>
+      </c>
+      <c r="N304" t="s" s="2">
         <v>1070</v>
-      </c>
-      <c r="N304" t="s" s="2">
-        <v>1071</v>
       </c>
       <c r="O304" s="2"/>
       <c r="P304" s="2"/>
@@ -36544,7 +36541,7 @@
         <v>74</v>
       </c>
       <c r="AG304" t="s" s="2">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="AH304" t="s" s="2">
         <v>75</v>
@@ -36564,10 +36561,10 @@
         <v>705</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" t="s" s="2">
@@ -36590,13 +36587,13 @@
         <v>83</v>
       </c>
       <c r="L305" t="s" s="2">
+        <v>1073</v>
+      </c>
+      <c r="M305" t="s" s="2">
         <v>1074</v>
       </c>
-      <c r="M305" t="s" s="2">
+      <c r="N305" t="s" s="2">
         <v>1075</v>
-      </c>
-      <c r="N305" t="s" s="2">
-        <v>1076</v>
       </c>
       <c r="O305" s="2"/>
       <c r="P305" s="2"/>
@@ -36620,34 +36617,34 @@
         <v>74</v>
       </c>
       <c r="X305" t="s" s="2">
+        <v>1076</v>
+      </c>
+      <c r="Y305" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z305" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA305" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB305" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC305" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD305" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE305" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF305" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG305" t="s" s="2">
         <v>1077</v>
-      </c>
-      <c r="Y305" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z305" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA305" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB305" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC305" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD305" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE305" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF305" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG305" t="s" s="2">
-        <v>1078</v>
       </c>
       <c r="AH305" t="s" s="2">
         <v>82</v>
@@ -36667,10 +36664,10 @@
         <v>705</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" t="s" s="2">
@@ -36696,13 +36693,13 @@
         <v>407</v>
       </c>
       <c r="M306" t="s" s="2">
+        <v>1079</v>
+      </c>
+      <c r="N306" t="s" s="2">
         <v>1080</v>
       </c>
-      <c r="N306" t="s" s="2">
+      <c r="O306" t="s" s="2">
         <v>1081</v>
-      </c>
-      <c r="O306" t="s" s="2">
-        <v>1082</v>
       </c>
       <c r="P306" s="2"/>
       <c r="Q306" t="s" s="2">
@@ -36731,11 +36728,11 @@
         <v>348</v>
       </c>
       <c r="Z306" t="s" s="2">
+        <v>1082</v>
+      </c>
+      <c r="AA306" t="s" s="2">
         <v>1083</v>
       </c>
-      <c r="AA306" t="s" s="2">
-        <v>1084</v>
-      </c>
       <c r="AB306" t="s" s="2">
         <v>74</v>
       </c>
@@ -36752,7 +36749,7 @@
         <v>74</v>
       </c>
       <c r="AG306" t="s" s="2">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AH306" t="s" s="2">
         <v>75</v>
@@ -36772,10 +36769,10 @@
         <v>705</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" t="s" s="2">
@@ -36801,16 +36798,16 @@
         <v>407</v>
       </c>
       <c r="M307" t="s" s="2">
+        <v>1085</v>
+      </c>
+      <c r="N307" t="s" s="2">
         <v>1086</v>
       </c>
-      <c r="N307" t="s" s="2">
+      <c r="O307" t="s" s="2">
         <v>1087</v>
       </c>
-      <c r="O307" t="s" s="2">
+      <c r="P307" t="s" s="2">
         <v>1088</v>
-      </c>
-      <c r="P307" t="s" s="2">
-        <v>1089</v>
       </c>
       <c r="Q307" t="s" s="2">
         <v>74</v>
@@ -36838,11 +36835,11 @@
         <v>348</v>
       </c>
       <c r="Z307" t="s" s="2">
+        <v>1089</v>
+      </c>
+      <c r="AA307" t="s" s="2">
         <v>1090</v>
       </c>
-      <c r="AA307" t="s" s="2">
-        <v>1091</v>
-      </c>
       <c r="AB307" t="s" s="2">
         <v>74</v>
       </c>
@@ -36859,7 +36856,7 @@
         <v>74</v>
       </c>
       <c r="AG307" t="s" s="2">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="AH307" t="s" s="2">
         <v>75</v>
@@ -36879,10 +36876,10 @@
         <v>705</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" t="s" s="2">
@@ -36982,10 +36979,10 @@
         <v>705</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" t="s" s="2">
@@ -37087,10 +37084,10 @@
         <v>705</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" t="s" s="2">
@@ -37192,13 +37189,13 @@
         <v>705</v>
       </c>
       <c r="B311" t="s" s="2">
+        <v>1094</v>
+      </c>
+      <c r="C311" t="s" s="2">
+        <v>1093</v>
+      </c>
+      <c r="D311" t="s" s="2">
         <v>1095</v>
-      </c>
-      <c r="C311" t="s" s="2">
-        <v>1094</v>
-      </c>
-      <c r="D311" t="s" s="2">
-        <v>1096</v>
       </c>
       <c r="E311" t="s" s="2">
         <v>74</v>
@@ -37261,7 +37258,7 @@
       </c>
       <c r="Z311" s="2"/>
       <c r="AA311" t="s" s="2">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="AB311" t="s" s="2">
         <v>74</v>
@@ -37299,10 +37296,10 @@
         <v>705</v>
       </c>
       <c r="B312" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="C312" t="s" s="2">
         <v>1098</v>
-      </c>
-      <c r="C312" t="s" s="2">
-        <v>1099</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" t="s" s="2">
@@ -37402,10 +37399,10 @@
         <v>705</v>
       </c>
       <c r="B313" t="s" s="2">
+        <v>1099</v>
+      </c>
+      <c r="C313" t="s" s="2">
         <v>1100</v>
-      </c>
-      <c r="C313" t="s" s="2">
-        <v>1101</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" t="s" s="2">
@@ -37507,10 +37504,10 @@
         <v>705</v>
       </c>
       <c r="B314" t="s" s="2">
+        <v>1101</v>
+      </c>
+      <c r="C314" t="s" s="2">
         <v>1102</v>
-      </c>
-      <c r="C314" t="s" s="2">
-        <v>1103</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" t="s" s="2">
@@ -37555,7 +37552,7 @@
         <v>74</v>
       </c>
       <c r="T314" t="s" s="2">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="U314" t="s" s="2">
         <v>74</v>
@@ -37614,10 +37611,10 @@
         <v>705</v>
       </c>
       <c r="B315" t="s" s="2">
+        <v>1104</v>
+      </c>
+      <c r="C315" t="s" s="2">
         <v>1105</v>
-      </c>
-      <c r="C315" t="s" s="2">
-        <v>1106</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" t="s" s="2">
@@ -37719,10 +37716,10 @@
         <v>705</v>
       </c>
       <c r="B316" t="s" s="2">
+        <v>1106</v>
+      </c>
+      <c r="C316" t="s" s="2">
         <v>1107</v>
-      </c>
-      <c r="C316" t="s" s="2">
-        <v>1108</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" t="s" s="2">
@@ -37824,10 +37821,10 @@
         <v>705</v>
       </c>
       <c r="B317" t="s" s="2">
+        <v>1108</v>
+      </c>
+      <c r="C317" t="s" s="2">
         <v>1109</v>
-      </c>
-      <c r="C317" t="s" s="2">
-        <v>1110</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" t="s" s="2">
@@ -37929,10 +37926,10 @@
         <v>705</v>
       </c>
       <c r="B318" t="s" s="2">
+        <v>1110</v>
+      </c>
+      <c r="C318" t="s" s="2">
         <v>1111</v>
-      </c>
-      <c r="C318" t="s" s="2">
-        <v>1112</v>
       </c>
       <c r="D318" s="2"/>
       <c r="E318" t="s" s="2">
@@ -38036,10 +38033,10 @@
         <v>705</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" t="s" s="2">
@@ -38143,10 +38140,10 @@
         <v>705</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="D320" s="2"/>
       <c r="E320" t="s" s="2">
@@ -38169,16 +38166,16 @@
         <v>74</v>
       </c>
       <c r="L320" t="s" s="2">
+        <v>1114</v>
+      </c>
+      <c r="M320" t="s" s="2">
         <v>1115</v>
       </c>
-      <c r="M320" t="s" s="2">
+      <c r="N320" t="s" s="2">
         <v>1116</v>
       </c>
-      <c r="N320" t="s" s="2">
+      <c r="O320" t="s" s="2">
         <v>1117</v>
-      </c>
-      <c r="O320" t="s" s="2">
-        <v>1118</v>
       </c>
       <c r="P320" s="2"/>
       <c r="Q320" t="s" s="2">
@@ -38228,7 +38225,7 @@
         <v>74</v>
       </c>
       <c r="AG320" t="s" s="2">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="AH320" t="s" s="2">
         <v>75</v>
@@ -38248,10 +38245,10 @@
         <v>705</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" t="s" s="2">
@@ -38274,16 +38271,16 @@
         <v>74</v>
       </c>
       <c r="L321" t="s" s="2">
+        <v>1119</v>
+      </c>
+      <c r="M321" t="s" s="2">
         <v>1120</v>
       </c>
-      <c r="M321" t="s" s="2">
+      <c r="N321" t="s" s="2">
         <v>1121</v>
       </c>
-      <c r="N321" t="s" s="2">
+      <c r="O321" t="s" s="2">
         <v>1122</v>
-      </c>
-      <c r="O321" t="s" s="2">
-        <v>1123</v>
       </c>
       <c r="P321" s="2"/>
       <c r="Q321" t="s" s="2">
@@ -38333,7 +38330,7 @@
         <v>74</v>
       </c>
       <c r="AG321" t="s" s="2">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AH321" t="s" s="2">
         <v>75</v>
@@ -38353,10 +38350,10 @@
         <v>705</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D322" s="2"/>
       <c r="E322" t="s" s="2">
@@ -38382,16 +38379,16 @@
         <v>137</v>
       </c>
       <c r="M322" t="s" s="2">
+        <v>1124</v>
+      </c>
+      <c r="N322" t="s" s="2">
         <v>1125</v>
       </c>
-      <c r="N322" t="s" s="2">
+      <c r="O322" t="s" s="2">
         <v>1126</v>
       </c>
-      <c r="O322" t="s" s="2">
+      <c r="P322" t="s" s="2">
         <v>1127</v>
-      </c>
-      <c r="P322" t="s" s="2">
-        <v>1128</v>
       </c>
       <c r="Q322" t="s" s="2">
         <v>74</v>
@@ -38440,7 +38437,7 @@
         <v>74</v>
       </c>
       <c r="AG322" t="s" s="2">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="AH322" t="s" s="2">
         <v>75</v>
@@ -38452,7 +38449,7 @@
         <v>74</v>
       </c>
       <c r="AK322" t="s" s="2">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="323">
@@ -38460,10 +38457,10 @@
         <v>705</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D323" s="2"/>
       <c r="E323" t="s" s="2">
@@ -38563,10 +38560,10 @@
         <v>705</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D324" s="2"/>
       <c r="E324" t="s" s="2">
@@ -38668,10 +38665,10 @@
         <v>705</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D325" s="2"/>
       <c r="E325" t="s" s="2">
@@ -38775,10 +38772,10 @@
         <v>705</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D326" s="2"/>
       <c r="E326" t="s" s="2">
@@ -38801,13 +38798,13 @@
         <v>74</v>
       </c>
       <c r="L326" t="s" s="2">
+        <v>1133</v>
+      </c>
+      <c r="M326" t="s" s="2">
         <v>1134</v>
       </c>
-      <c r="M326" t="s" s="2">
+      <c r="N326" t="s" s="2">
         <v>1135</v>
-      </c>
-      <c r="N326" t="s" s="2">
-        <v>1136</v>
       </c>
       <c r="O326" s="2"/>
       <c r="P326" s="2"/>
@@ -38858,7 +38855,7 @@
         <v>74</v>
       </c>
       <c r="AG326" t="s" s="2">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="AH326" t="s" s="2">
         <v>75</v>
@@ -38867,7 +38864,7 @@
         <v>82</v>
       </c>
       <c r="AJ326" t="s" s="2">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AK326" t="s" s="2">
         <v>95</v>
@@ -38878,10 +38875,10 @@
         <v>705</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" t="s" s="2">
@@ -38904,13 +38901,13 @@
         <v>74</v>
       </c>
       <c r="L327" t="s" s="2">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="M327" t="s" s="2">
+        <v>1138</v>
+      </c>
+      <c r="N327" t="s" s="2">
         <v>1139</v>
-      </c>
-      <c r="N327" t="s" s="2">
-        <v>1140</v>
       </c>
       <c r="O327" s="2"/>
       <c r="P327" s="2"/>
@@ -38961,7 +38958,7 @@
         <v>74</v>
       </c>
       <c r="AG327" t="s" s="2">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="AH327" t="s" s="2">
         <v>75</v>
@@ -38970,7 +38967,7 @@
         <v>82</v>
       </c>
       <c r="AJ327" t="s" s="2">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AK327" t="s" s="2">
         <v>95</v>
@@ -38981,10 +38978,10 @@
         <v>705</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" t="s" s="2">
@@ -39010,16 +39007,16 @@
         <v>407</v>
       </c>
       <c r="M328" t="s" s="2">
+        <v>1141</v>
+      </c>
+      <c r="N328" t="s" s="2">
         <v>1142</v>
       </c>
-      <c r="N328" t="s" s="2">
+      <c r="O328" t="s" s="2">
         <v>1143</v>
       </c>
-      <c r="O328" t="s" s="2">
+      <c r="P328" t="s" s="2">
         <v>1144</v>
-      </c>
-      <c r="P328" t="s" s="2">
-        <v>1145</v>
       </c>
       <c r="Q328" t="s" s="2">
         <v>74</v>
@@ -39047,11 +39044,11 @@
         <v>107</v>
       </c>
       <c r="Z328" t="s" s="2">
+        <v>1145</v>
+      </c>
+      <c r="AA328" t="s" s="2">
         <v>1146</v>
       </c>
-      <c r="AA328" t="s" s="2">
-        <v>1147</v>
-      </c>
       <c r="AB328" t="s" s="2">
         <v>74</v>
       </c>
@@ -39068,7 +39065,7 @@
         <v>74</v>
       </c>
       <c r="AG328" t="s" s="2">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="AH328" t="s" s="2">
         <v>75</v>
@@ -39088,10 +39085,10 @@
         <v>705</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D329" s="2"/>
       <c r="E329" t="s" s="2">
@@ -39117,16 +39114,16 @@
         <v>407</v>
       </c>
       <c r="M329" t="s" s="2">
+        <v>1148</v>
+      </c>
+      <c r="N329" t="s" s="2">
         <v>1149</v>
       </c>
-      <c r="N329" t="s" s="2">
+      <c r="O329" t="s" s="2">
         <v>1150</v>
       </c>
-      <c r="O329" t="s" s="2">
+      <c r="P329" t="s" s="2">
         <v>1151</v>
-      </c>
-      <c r="P329" t="s" s="2">
-        <v>1152</v>
       </c>
       <c r="Q329" t="s" s="2">
         <v>74</v>
@@ -39154,11 +39151,11 @@
         <v>348</v>
       </c>
       <c r="Z329" t="s" s="2">
+        <v>1152</v>
+      </c>
+      <c r="AA329" t="s" s="2">
         <v>1153</v>
       </c>
-      <c r="AA329" t="s" s="2">
-        <v>1154</v>
-      </c>
       <c r="AB329" t="s" s="2">
         <v>74</v>
       </c>
@@ -39175,7 +39172,7 @@
         <v>74</v>
       </c>
       <c r="AG329" t="s" s="2">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AH329" t="s" s="2">
         <v>75</v>
@@ -39195,10 +39192,10 @@
         <v>705</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D330" s="2"/>
       <c r="E330" t="s" s="2">
@@ -39221,17 +39218,17 @@
         <v>74</v>
       </c>
       <c r="L330" t="s" s="2">
+        <v>1155</v>
+      </c>
+      <c r="M330" t="s" s="2">
         <v>1156</v>
       </c>
-      <c r="M330" t="s" s="2">
+      <c r="N330" t="s" s="2">
         <v>1157</v>
-      </c>
-      <c r="N330" t="s" s="2">
-        <v>1158</v>
       </c>
       <c r="O330" s="2"/>
       <c r="P330" t="s" s="2">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="Q330" t="s" s="2">
         <v>74</v>
@@ -39280,7 +39277,7 @@
         <v>74</v>
       </c>
       <c r="AG330" t="s" s="2">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="AH330" t="s" s="2">
         <v>75</v>
@@ -39300,10 +39297,10 @@
         <v>705</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="D331" s="2"/>
       <c r="E331" t="s" s="2">
@@ -39329,10 +39326,10 @@
         <v>142</v>
       </c>
       <c r="M331" t="s" s="2">
+        <v>1160</v>
+      </c>
+      <c r="N331" t="s" s="2">
         <v>1161</v>
-      </c>
-      <c r="N331" t="s" s="2">
-        <v>1162</v>
       </c>
       <c r="O331" s="2"/>
       <c r="P331" s="2"/>
@@ -39383,7 +39380,7 @@
         <v>74</v>
       </c>
       <c r="AG331" t="s" s="2">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="AH331" t="s" s="2">
         <v>75</v>
@@ -39403,10 +39400,10 @@
         <v>705</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="D332" s="2"/>
       <c r="E332" t="s" s="2">
@@ -39429,16 +39426,16 @@
         <v>83</v>
       </c>
       <c r="L332" t="s" s="2">
+        <v>1163</v>
+      </c>
+      <c r="M332" t="s" s="2">
         <v>1164</v>
       </c>
-      <c r="M332" t="s" s="2">
+      <c r="N332" t="s" s="2">
         <v>1165</v>
       </c>
-      <c r="N332" t="s" s="2">
+      <c r="O332" t="s" s="2">
         <v>1166</v>
-      </c>
-      <c r="O332" t="s" s="2">
-        <v>1167</v>
       </c>
       <c r="P332" s="2"/>
       <c r="Q332" t="s" s="2">
@@ -39488,7 +39485,7 @@
         <v>74</v>
       </c>
       <c r="AG332" t="s" s="2">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="AH332" t="s" s="2">
         <v>75</v>
@@ -39508,10 +39505,10 @@
         <v>705</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D333" s="2"/>
       <c r="E333" t="s" s="2">
@@ -39534,16 +39531,16 @@
         <v>83</v>
       </c>
       <c r="L333" t="s" s="2">
+        <v>1168</v>
+      </c>
+      <c r="M333" t="s" s="2">
         <v>1169</v>
       </c>
-      <c r="M333" t="s" s="2">
+      <c r="N333" t="s" s="2">
         <v>1170</v>
       </c>
-      <c r="N333" t="s" s="2">
+      <c r="O333" t="s" s="2">
         <v>1171</v>
-      </c>
-      <c r="O333" t="s" s="2">
-        <v>1172</v>
       </c>
       <c r="P333" s="2"/>
       <c r="Q333" t="s" s="2">
@@ -39593,7 +39590,7 @@
         <v>74</v>
       </c>
       <c r="AG333" t="s" s="2">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="AH333" t="s" s="2">
         <v>75</v>
@@ -39613,10 +39610,10 @@
         <v>705</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D334" s="2"/>
       <c r="E334" t="s" s="2">
@@ -39642,16 +39639,16 @@
         <v>137</v>
       </c>
       <c r="M334" t="s" s="2">
+        <v>1173</v>
+      </c>
+      <c r="N334" t="s" s="2">
         <v>1174</v>
       </c>
-      <c r="N334" t="s" s="2">
+      <c r="O334" t="s" s="2">
         <v>1175</v>
       </c>
-      <c r="O334" t="s" s="2">
+      <c r="P334" t="s" s="2">
         <v>1176</v>
-      </c>
-      <c r="P334" t="s" s="2">
-        <v>1177</v>
       </c>
       <c r="Q334" t="s" s="2">
         <v>74</v>
@@ -39700,7 +39697,7 @@
         <v>74</v>
       </c>
       <c r="AG334" t="s" s="2">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="AH334" t="s" s="2">
         <v>75</v>
@@ -39720,10 +39717,10 @@
         <v>705</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D335" s="2"/>
       <c r="E335" t="s" s="2">
@@ -39823,10 +39820,10 @@
         <v>705</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D336" s="2"/>
       <c r="E336" t="s" s="2">
@@ -39928,10 +39925,10 @@
         <v>705</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="D337" s="2"/>
       <c r="E337" t="s" s="2">
@@ -40035,10 +40032,10 @@
         <v>705</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="D338" s="2"/>
       <c r="E338" t="s" s="2">
@@ -40064,13 +40061,13 @@
         <v>407</v>
       </c>
       <c r="M338" t="s" s="2">
+        <v>1181</v>
+      </c>
+      <c r="N338" t="s" s="2">
         <v>1182</v>
       </c>
-      <c r="N338" t="s" s="2">
+      <c r="O338" t="s" s="2">
         <v>1183</v>
-      </c>
-      <c r="O338" t="s" s="2">
-        <v>1184</v>
       </c>
       <c r="P338" t="s" s="2">
         <v>861</v>
@@ -40122,7 +40119,7 @@
         <v>74</v>
       </c>
       <c r="AG338" t="s" s="2">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AH338" t="s" s="2">
         <v>82</v>
@@ -40142,10 +40139,10 @@
         <v>705</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D339" s="2"/>
       <c r="E339" t="s" s="2">
@@ -40245,10 +40242,10 @@
         <v>705</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D340" s="2"/>
       <c r="E340" t="s" s="2">
@@ -40350,10 +40347,10 @@
         <v>705</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D341" s="2"/>
       <c r="E341" t="s" s="2">
@@ -40455,10 +40452,10 @@
         <v>705</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D342" t="s" s="2">
         <v>869</v>
@@ -40564,10 +40561,10 @@
         <v>705</v>
       </c>
       <c r="B343" t="s" s="2">
+        <v>1188</v>
+      </c>
+      <c r="C343" t="s" s="2">
         <v>1189</v>
-      </c>
-      <c r="C343" t="s" s="2">
-        <v>1190</v>
       </c>
       <c r="D343" s="2"/>
       <c r="E343" t="s" s="2">
@@ -40667,10 +40664,10 @@
         <v>705</v>
       </c>
       <c r="B344" t="s" s="2">
+        <v>1190</v>
+      </c>
+      <c r="C344" t="s" s="2">
         <v>1191</v>
-      </c>
-      <c r="C344" t="s" s="2">
-        <v>1192</v>
       </c>
       <c r="D344" s="2"/>
       <c r="E344" t="s" s="2">
@@ -40772,10 +40769,10 @@
         <v>705</v>
       </c>
       <c r="B345" t="s" s="2">
+        <v>1192</v>
+      </c>
+      <c r="C345" t="s" s="2">
         <v>1193</v>
-      </c>
-      <c r="C345" t="s" s="2">
-        <v>1194</v>
       </c>
       <c r="D345" s="2"/>
       <c r="E345" t="s" s="2">
@@ -40879,10 +40876,10 @@
         <v>705</v>
       </c>
       <c r="B346" t="s" s="2">
+        <v>1194</v>
+      </c>
+      <c r="C346" t="s" s="2">
         <v>1195</v>
-      </c>
-      <c r="C346" t="s" s="2">
-        <v>1196</v>
       </c>
       <c r="D346" s="2"/>
       <c r="E346" t="s" s="2">
@@ -40984,10 +40981,10 @@
         <v>705</v>
       </c>
       <c r="B347" t="s" s="2">
+        <v>1196</v>
+      </c>
+      <c r="C347" t="s" s="2">
         <v>1197</v>
-      </c>
-      <c r="C347" t="s" s="2">
-        <v>1198</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" t="s" s="2">
@@ -41089,10 +41086,10 @@
         <v>705</v>
       </c>
       <c r="B348" t="s" s="2">
+        <v>1198</v>
+      </c>
+      <c r="C348" t="s" s="2">
         <v>1199</v>
-      </c>
-      <c r="C348" t="s" s="2">
-        <v>1200</v>
       </c>
       <c r="D348" s="2"/>
       <c r="E348" t="s" s="2">
@@ -41194,10 +41191,10 @@
         <v>705</v>
       </c>
       <c r="B349" t="s" s="2">
+        <v>1200</v>
+      </c>
+      <c r="C349" t="s" s="2">
         <v>1201</v>
-      </c>
-      <c r="C349" t="s" s="2">
-        <v>1202</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" t="s" s="2">
@@ -41301,10 +41298,10 @@
         <v>705</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D350" t="s" s="2">
         <v>886</v>
@@ -41410,10 +41407,10 @@
         <v>705</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="D351" s="2"/>
       <c r="E351" t="s" s="2">
@@ -41513,10 +41510,10 @@
         <v>705</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D352" s="2"/>
       <c r="E352" t="s" s="2">
@@ -41618,10 +41615,10 @@
         <v>705</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="D353" s="2"/>
       <c r="E353" t="s" s="2">
@@ -41725,10 +41722,10 @@
         <v>705</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D354" s="2"/>
       <c r="E354" t="s" s="2">
@@ -41830,10 +41827,10 @@
         <v>705</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D355" s="2"/>
       <c r="E355" t="s" s="2">
@@ -41935,10 +41932,10 @@
         <v>705</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" t="s" s="2">
@@ -42040,10 +42037,10 @@
         <v>705</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D357" s="2"/>
       <c r="E357" t="s" s="2">
@@ -42147,10 +42144,10 @@
         <v>705</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D358" t="s" s="2">
         <v>897</v>
@@ -42256,10 +42253,10 @@
         <v>705</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="D359" s="2"/>
       <c r="E359" t="s" s="2">
@@ -42359,10 +42356,10 @@
         <v>705</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D360" s="2"/>
       <c r="E360" t="s" s="2">
@@ -42464,10 +42461,10 @@
         <v>705</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="D361" s="2"/>
       <c r="E361" t="s" s="2">
@@ -42571,10 +42568,10 @@
         <v>705</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D362" s="2"/>
       <c r="E362" t="s" s="2">
@@ -42676,10 +42673,10 @@
         <v>705</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D363" s="2"/>
       <c r="E363" t="s" s="2">
@@ -42781,10 +42778,10 @@
         <v>705</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D364" s="2"/>
       <c r="E364" t="s" s="2">
@@ -42886,10 +42883,10 @@
         <v>705</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D365" s="2"/>
       <c r="E365" t="s" s="2">
@@ -42993,10 +42990,10 @@
         <v>705</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D366" t="s" s="2">
         <v>908</v>
@@ -43102,10 +43099,10 @@
         <v>705</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="D367" s="2"/>
       <c r="E367" t="s" s="2">
@@ -43205,10 +43202,10 @@
         <v>705</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D368" s="2"/>
       <c r="E368" t="s" s="2">
@@ -43310,10 +43307,10 @@
         <v>705</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="D369" s="2"/>
       <c r="E369" t="s" s="2">
@@ -43417,10 +43414,10 @@
         <v>705</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D370" s="2"/>
       <c r="E370" t="s" s="2">
@@ -43522,10 +43519,10 @@
         <v>705</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D371" s="2"/>
       <c r="E371" t="s" s="2">
@@ -43627,10 +43624,10 @@
         <v>705</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D372" s="2"/>
       <c r="E372" t="s" s="2">
@@ -43732,10 +43729,10 @@
         <v>705</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D373" s="2"/>
       <c r="E373" t="s" s="2">
@@ -43839,10 +43836,10 @@
         <v>705</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D374" t="s" s="2">
         <v>17</v>
@@ -43948,10 +43945,10 @@
         <v>705</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="D375" s="2"/>
       <c r="E375" t="s" s="2">
@@ -44051,10 +44048,10 @@
         <v>705</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D376" s="2"/>
       <c r="E376" t="s" s="2">
@@ -44156,10 +44153,10 @@
         <v>705</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" t="s" s="2">
@@ -44263,10 +44260,10 @@
         <v>705</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" t="s" s="2">
@@ -44368,10 +44365,10 @@
         <v>705</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D379" s="2"/>
       <c r="E379" t="s" s="2">
@@ -44473,10 +44470,10 @@
         <v>705</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D380" s="2"/>
       <c r="E380" t="s" s="2">
@@ -44578,10 +44575,10 @@
         <v>705</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D381" s="2"/>
       <c r="E381" t="s" s="2">
@@ -44685,10 +44682,10 @@
         <v>705</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D382" t="s" s="2">
         <v>929</v>
@@ -44716,7 +44713,7 @@
         <v>336</v>
       </c>
       <c r="M382" t="s" s="2">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="N382" t="s" s="2">
         <v>458</v>
@@ -44794,10 +44791,10 @@
         <v>705</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" t="s" s="2">
@@ -44897,10 +44894,10 @@
         <v>705</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" t="s" s="2">
@@ -45002,10 +44999,10 @@
         <v>705</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="D385" s="2"/>
       <c r="E385" t="s" s="2">
@@ -45109,10 +45106,10 @@
         <v>705</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D386" s="2"/>
       <c r="E386" t="s" s="2">
@@ -45214,10 +45211,10 @@
         <v>705</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D387" s="2"/>
       <c r="E387" t="s" s="2">
@@ -45319,10 +45316,10 @@
         <v>705</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D388" s="2"/>
       <c r="E388" t="s" s="2">
@@ -45424,10 +45421,10 @@
         <v>705</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D389" s="2"/>
       <c r="E389" t="s" s="2">
@@ -45531,10 +45528,10 @@
         <v>705</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="D390" s="2"/>
       <c r="E390" t="s" s="2">
@@ -45638,10 +45635,10 @@
         <v>705</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="D391" s="2"/>
       <c r="E391" t="s" s="2">
@@ -45664,19 +45661,19 @@
         <v>83</v>
       </c>
       <c r="L391" t="s" s="2">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="M391" t="s" s="2">
+        <v>1245</v>
+      </c>
+      <c r="N391" t="s" s="2">
+        <v>990</v>
+      </c>
+      <c r="O391" t="s" s="2">
         <v>1246</v>
       </c>
-      <c r="N391" t="s" s="2">
-        <v>991</v>
-      </c>
-      <c r="O391" t="s" s="2">
-        <v>1247</v>
-      </c>
       <c r="P391" t="s" s="2">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="Q391" t="s" s="2">
         <v>74</v>
@@ -45723,7 +45720,7 @@
         <v>171</v>
       </c>
       <c r="AG391" t="s" s="2">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="AH391" t="s" s="2">
         <v>75</v>
@@ -45743,13 +45740,13 @@
         <v>705</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="D392" t="s" s="2">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E392" t="s" s="2">
         <v>74</v>
@@ -45771,19 +45768,19 @@
         <v>83</v>
       </c>
       <c r="L392" t="s" s="2">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="M392" t="s" s="2">
+        <v>1245</v>
+      </c>
+      <c r="N392" t="s" s="2">
+        <v>990</v>
+      </c>
+      <c r="O392" t="s" s="2">
         <v>1246</v>
       </c>
-      <c r="N392" t="s" s="2">
-        <v>991</v>
-      </c>
-      <c r="O392" t="s" s="2">
-        <v>1247</v>
-      </c>
       <c r="P392" t="s" s="2">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="Q392" t="s" s="2">
         <v>74</v>
@@ -45832,7 +45829,7 @@
         <v>74</v>
       </c>
       <c r="AG392" t="s" s="2">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="AH392" t="s" s="2">
         <v>75</v>
@@ -45852,10 +45849,10 @@
         <v>705</v>
       </c>
       <c r="B393" t="s" s="2">
+        <v>1248</v>
+      </c>
+      <c r="C393" t="s" s="2">
         <v>1249</v>
-      </c>
-      <c r="C393" t="s" s="2">
-        <v>1250</v>
       </c>
       <c r="D393" s="2"/>
       <c r="E393" t="s" s="2">
@@ -45955,10 +45952,10 @@
         <v>705</v>
       </c>
       <c r="B394" t="s" s="2">
+        <v>1250</v>
+      </c>
+      <c r="C394" t="s" s="2">
         <v>1251</v>
-      </c>
-      <c r="C394" t="s" s="2">
-        <v>1252</v>
       </c>
       <c r="D394" s="2"/>
       <c r="E394" t="s" s="2">
@@ -46060,10 +46057,10 @@
         <v>705</v>
       </c>
       <c r="B395" t="s" s="2">
+        <v>1252</v>
+      </c>
+      <c r="C395" t="s" s="2">
         <v>1253</v>
-      </c>
-      <c r="C395" t="s" s="2">
-        <v>1254</v>
       </c>
       <c r="D395" s="2"/>
       <c r="E395" t="s" s="2">
@@ -46089,16 +46086,16 @@
         <v>201</v>
       </c>
       <c r="M395" t="s" s="2">
+        <v>1003</v>
+      </c>
+      <c r="N395" t="s" s="2">
         <v>1004</v>
       </c>
-      <c r="N395" t="s" s="2">
+      <c r="O395" t="s" s="2">
         <v>1005</v>
       </c>
-      <c r="O395" t="s" s="2">
+      <c r="P395" t="s" s="2">
         <v>1006</v>
-      </c>
-      <c r="P395" t="s" s="2">
-        <v>1007</v>
       </c>
       <c r="Q395" t="s" s="2">
         <v>74</v>
@@ -46147,7 +46144,7 @@
         <v>74</v>
       </c>
       <c r="AG395" t="s" s="2">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AH395" t="s" s="2">
         <v>75</v>
@@ -46167,10 +46164,10 @@
         <v>705</v>
       </c>
       <c r="B396" t="s" s="2">
+        <v>1254</v>
+      </c>
+      <c r="C396" t="s" s="2">
         <v>1255</v>
-      </c>
-      <c r="C396" t="s" s="2">
-        <v>1256</v>
       </c>
       <c r="D396" s="2"/>
       <c r="E396" t="s" s="2">
@@ -46196,20 +46193,20 @@
         <v>103</v>
       </c>
       <c r="M396" t="s" s="2">
+        <v>1010</v>
+      </c>
+      <c r="N396" t="s" s="2">
         <v>1011</v>
-      </c>
-      <c r="N396" t="s" s="2">
-        <v>1012</v>
       </c>
       <c r="O396" s="2"/>
       <c r="P396" t="s" s="2">
+        <v>1012</v>
+      </c>
+      <c r="Q396" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R396" t="s" s="2">
         <v>1013</v>
-      </c>
-      <c r="Q396" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R396" t="s" s="2">
-        <v>1014</v>
       </c>
       <c r="S396" t="s" s="2">
         <v>74</v>
@@ -46233,28 +46230,28 @@
         <v>121</v>
       </c>
       <c r="Z396" t="s" s="2">
+        <v>1014</v>
+      </c>
+      <c r="AA396" t="s" s="2">
         <v>1015</v>
       </c>
-      <c r="AA396" t="s" s="2">
+      <c r="AB396" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC396" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD396" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE396" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF396" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG396" t="s" s="2">
         <v>1016</v>
-      </c>
-      <c r="AB396" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC396" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD396" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE396" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF396" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG396" t="s" s="2">
-        <v>1017</v>
       </c>
       <c r="AH396" t="s" s="2">
         <v>75</v>
@@ -46274,10 +46271,10 @@
         <v>705</v>
       </c>
       <c r="B397" t="s" s="2">
+        <v>1256</v>
+      </c>
+      <c r="C397" t="s" s="2">
         <v>1257</v>
-      </c>
-      <c r="C397" t="s" s="2">
-        <v>1258</v>
       </c>
       <c r="D397" s="2"/>
       <c r="E397" t="s" s="2">
@@ -46303,14 +46300,14 @@
         <v>142</v>
       </c>
       <c r="M397" t="s" s="2">
+        <v>1019</v>
+      </c>
+      <c r="N397" t="s" s="2">
         <v>1020</v>
-      </c>
-      <c r="N397" t="s" s="2">
-        <v>1021</v>
       </c>
       <c r="O397" s="2"/>
       <c r="P397" t="s" s="2">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="Q397" t="s" s="2">
         <v>74</v>
@@ -46359,7 +46356,7 @@
         <v>74</v>
       </c>
       <c r="AG397" t="s" s="2">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AH397" t="s" s="2">
         <v>75</v>
@@ -46379,10 +46376,10 @@
         <v>705</v>
       </c>
       <c r="B398" t="s" s="2">
+        <v>1258</v>
+      </c>
+      <c r="C398" t="s" s="2">
         <v>1259</v>
-      </c>
-      <c r="C398" t="s" s="2">
-        <v>1260</v>
       </c>
       <c r="D398" s="2"/>
       <c r="E398" t="s" s="2">
@@ -46408,14 +46405,14 @@
         <v>97</v>
       </c>
       <c r="M398" t="s" s="2">
+        <v>1025</v>
+      </c>
+      <c r="N398" t="s" s="2">
         <v>1026</v>
-      </c>
-      <c r="N398" t="s" s="2">
-        <v>1027</v>
       </c>
       <c r="O398" s="2"/>
       <c r="P398" t="s" s="2">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="Q398" t="s" s="2">
         <v>74</v>
@@ -46425,55 +46422,55 @@
         <v>74</v>
       </c>
       <c r="T398" t="s" s="2">
+        <v>1028</v>
+      </c>
+      <c r="U398" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V398" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W398" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X398" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y398" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z398" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA398" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB398" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC398" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD398" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE398" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF398" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG398" t="s" s="2">
         <v>1029</v>
       </c>
-      <c r="U398" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V398" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W398" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X398" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y398" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z398" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA398" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB398" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC398" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD398" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE398" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF398" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG398" t="s" s="2">
+      <c r="AH398" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI398" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ398" t="s" s="2">
         <v>1030</v>
-      </c>
-      <c r="AH398" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI398" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ398" t="s" s="2">
-        <v>1031</v>
       </c>
       <c r="AK398" t="s" s="2">
         <v>95</v>
@@ -46484,10 +46481,10 @@
         <v>705</v>
       </c>
       <c r="B399" t="s" s="2">
+        <v>1260</v>
+      </c>
+      <c r="C399" t="s" s="2">
         <v>1261</v>
-      </c>
-      <c r="C399" t="s" s="2">
-        <v>1262</v>
       </c>
       <c r="D399" s="2"/>
       <c r="E399" t="s" s="2">
@@ -46513,16 +46510,16 @@
         <v>103</v>
       </c>
       <c r="M399" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="N399" t="s" s="2">
         <v>1034</v>
       </c>
-      <c r="N399" t="s" s="2">
+      <c r="O399" t="s" s="2">
         <v>1035</v>
       </c>
-      <c r="O399" t="s" s="2">
+      <c r="P399" t="s" s="2">
         <v>1036</v>
-      </c>
-      <c r="P399" t="s" s="2">
-        <v>1037</v>
       </c>
       <c r="Q399" t="s" s="2">
         <v>74</v>
@@ -46571,7 +46568,7 @@
         <v>74</v>
       </c>
       <c r="AG399" t="s" s="2">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="AH399" t="s" s="2">
         <v>75</v>
@@ -46591,10 +46588,10 @@
         <v>705</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D400" s="2"/>
       <c r="E400" t="s" s="2">
@@ -46620,16 +46617,16 @@
         <v>407</v>
       </c>
       <c r="M400" t="s" s="2">
+        <v>1263</v>
+      </c>
+      <c r="N400" t="s" s="2">
         <v>1264</v>
       </c>
-      <c r="N400" t="s" s="2">
+      <c r="O400" t="s" s="2">
         <v>1265</v>
       </c>
-      <c r="O400" t="s" s="2">
-        <v>1266</v>
-      </c>
       <c r="P400" t="s" s="2">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="Q400" t="s" s="2">
         <v>74</v>
@@ -46657,37 +46654,37 @@
         <v>340</v>
       </c>
       <c r="Z400" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="AA400" t="s" s="2">
         <v>1044</v>
       </c>
-      <c r="AA400" t="s" s="2">
+      <c r="AB400" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC400" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD400" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE400" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF400" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG400" t="s" s="2">
+        <v>1262</v>
+      </c>
+      <c r="AH400" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI400" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ400" t="s" s="2">
         <v>1045</v>
-      </c>
-      <c r="AB400" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC400" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD400" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE400" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF400" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG400" t="s" s="2">
-        <v>1263</v>
-      </c>
-      <c r="AH400" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI400" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ400" t="s" s="2">
-        <v>1046</v>
       </c>
       <c r="AK400" t="s" s="2">
         <v>95</v>
@@ -46698,14 +46695,14 @@
         <v>705</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="D401" s="2"/>
       <c r="E401" t="s" s="2">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F401" s="2"/>
       <c r="G401" t="s" s="2">
@@ -46727,16 +46724,16 @@
         <v>407</v>
       </c>
       <c r="M401" t="s" s="2">
+        <v>1048</v>
+      </c>
+      <c r="N401" t="s" s="2">
         <v>1049</v>
       </c>
-      <c r="N401" t="s" s="2">
+      <c r="O401" t="s" s="2">
         <v>1050</v>
       </c>
-      <c r="O401" t="s" s="2">
+      <c r="P401" t="s" s="2">
         <v>1051</v>
-      </c>
-      <c r="P401" t="s" s="2">
-        <v>1052</v>
       </c>
       <c r="Q401" t="s" s="2">
         <v>74</v>
@@ -46764,11 +46761,11 @@
         <v>340</v>
       </c>
       <c r="Z401" t="s" s="2">
+        <v>1052</v>
+      </c>
+      <c r="AA401" t="s" s="2">
         <v>1053</v>
       </c>
-      <c r="AA401" t="s" s="2">
-        <v>1054</v>
-      </c>
       <c r="AB401" t="s" s="2">
         <v>74</v>
       </c>
@@ -46785,7 +46782,7 @@
         <v>74</v>
       </c>
       <c r="AG401" t="s" s="2">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="AH401" t="s" s="2">
         <v>75</v>
@@ -46805,10 +46802,10 @@
         <v>705</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="D402" s="2"/>
       <c r="E402" t="s" s="2">
@@ -46834,16 +46831,16 @@
         <v>77</v>
       </c>
       <c r="M402" t="s" s="2">
+        <v>1268</v>
+      </c>
+      <c r="N402" t="s" s="2">
         <v>1269</v>
       </c>
-      <c r="N402" t="s" s="2">
-        <v>1270</v>
-      </c>
       <c r="O402" t="s" s="2">
+        <v>1126</v>
+      </c>
+      <c r="P402" t="s" s="2">
         <v>1127</v>
-      </c>
-      <c r="P402" t="s" s="2">
-        <v>1128</v>
       </c>
       <c r="Q402" t="s" s="2">
         <v>74</v>
@@ -46892,7 +46889,7 @@
         <v>74</v>
       </c>
       <c r="AG402" t="s" s="2">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="AH402" t="s" s="2">
         <v>75</v>
